--- a/excel/incre_flash_attention_log_analysis.xlsx
+++ b/excel/incre_flash_attention_log_analysis.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -465,6 +465,11 @@
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>数量</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>归属</t>
         </is>
       </c>
     </row>
@@ -559,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -601,6 +606,11 @@
           <t>日志类型</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -627,6 +637,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -653,6 +668,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -679,6 +699,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -705,6 +730,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -731,6 +761,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -757,6 +792,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -783,6 +823,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -809,6 +854,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -835,6 +885,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -861,6 +916,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -887,6 +947,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -913,6 +978,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -939,6 +1009,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -965,6 +1040,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -991,6 +1071,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1017,6 +1102,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1043,6 +1133,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1069,6 +1164,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1095,6 +1195,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1121,6 +1226,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1147,6 +1257,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1173,6 +1288,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1199,6 +1319,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1225,6 +1350,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1251,6 +1381,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1277,6 +1412,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -1303,6 +1443,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1329,6 +1474,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1355,6 +1505,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1381,6 +1536,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -1407,6 +1567,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -1433,6 +1598,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -1459,6 +1629,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -1485,6 +1660,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -1511,6 +1691,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -1537,6 +1722,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -1563,6 +1753,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -1589,6 +1784,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -1615,6 +1815,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -1641,6 +1846,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -1667,6 +1877,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -1693,6 +1908,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -1719,6 +1939,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -1745,6 +1970,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -1771,6 +2001,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -1797,6 +2032,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -1823,6 +2063,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -1849,6 +2094,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -1875,6 +2125,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -1901,6 +2156,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -1927,6 +2187,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -1953,6 +2218,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -1979,6 +2249,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -2005,6 +2280,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -2031,6 +2311,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -2057,6 +2342,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -2083,6 +2373,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -2109,6 +2404,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -2135,6 +2435,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -2161,6 +2466,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -2187,6 +2497,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -2213,6 +2528,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -2239,6 +2559,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -2265,6 +2590,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -2291,6 +2621,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -2317,6 +2652,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -2343,6 +2683,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -2369,6 +2714,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -2395,6 +2745,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -2421,6 +2776,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -2447,6 +2807,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -2473,6 +2838,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -2499,6 +2869,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -2525,6 +2900,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -2551,6 +2931,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -2577,6 +2962,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -2603,6 +2993,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -2629,6 +3024,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -2655,6 +3055,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -2681,6 +3086,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -2707,6 +3113,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -2733,6 +3140,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -2759,6 +3167,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -2785,6 +3194,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -2811,6 +3221,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -2837,6 +3248,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -2863,6 +3275,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -2889,6 +3302,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -2915,6 +3329,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -2941,6 +3356,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -2967,6 +3383,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -2993,6 +3410,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -3019,6 +3437,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -3045,6 +3464,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -3071,6 +3491,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -3097,6 +3518,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -3123,6 +3545,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -3149,6 +3572,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -3175,6 +3599,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -3201,6 +3626,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -3227,6 +3653,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -3253,6 +3680,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -3279,6 +3707,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -3305,6 +3734,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -3331,6 +3761,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -3357,6 +3788,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -3383,6 +3815,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -3409,6 +3842,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -3435,6 +3869,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -3461,6 +3896,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -3487,6 +3923,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -3513,6 +3950,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -3539,6 +3977,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -3565,6 +4004,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -3591,6 +4031,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -3617,6 +4058,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -3643,6 +4085,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -3669,6 +4112,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -3695,6 +4139,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -3721,6 +4166,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -3747,6 +4193,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -3773,6 +4220,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -3799,6 +4247,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -3825,6 +4274,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -3851,6 +4301,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -3877,6 +4328,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -3903,6 +4355,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -3929,6 +4382,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -3955,6 +4409,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -3981,6 +4436,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -4007,6 +4463,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
@@ -4033,6 +4490,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -4059,6 +4517,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -4085,6 +4544,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -4111,6 +4571,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
@@ -4137,6 +4598,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -4163,6 +4625,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -4189,6 +4652,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -4215,6 +4679,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -4241,6 +4706,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -4267,6 +4733,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -4293,6 +4760,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4305,7 +4773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -4347,6 +4815,11 @@
           <t>日志类型</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -4373,6 +4846,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -4399,6 +4873,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -4425,6 +4900,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -4451,6 +4927,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -4477,6 +4954,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -4503,6 +4981,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -4529,6 +5008,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -4555,6 +5035,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -4581,6 +5062,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -4607,6 +5093,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -4633,6 +5124,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -4659,6 +5155,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -4685,6 +5186,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -4711,6 +5217,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -4737,6 +5248,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -4763,6 +5279,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -4789,6 +5310,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -4815,6 +5341,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -4841,6 +5372,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -4867,6 +5403,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -4893,6 +5434,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -4919,6 +5465,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -4945,6 +5496,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -4971,6 +5527,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -4997,6 +5558,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -5023,6 +5589,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -5049,6 +5620,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -5075,6 +5651,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -5101,6 +5682,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -5127,6 +5713,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -5153,6 +5744,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -5179,6 +5775,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -5205,6 +5806,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -5231,6 +5837,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -5257,6 +5868,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -5283,6 +5899,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -5309,6 +5930,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -5335,6 +5957,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -5361,6 +5984,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -5387,6 +6011,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -5413,6 +6038,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -5439,6 +6065,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -5465,6 +6096,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -5491,6 +6127,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -5517,6 +6158,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -5543,6 +6189,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -5569,6 +6220,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -5595,6 +6251,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -5621,6 +6282,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -5647,6 +6313,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -5673,6 +6344,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -5699,6 +6375,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -5725,6 +6406,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -5751,6 +6437,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -5777,6 +6468,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -5803,6 +6499,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -5829,6 +6530,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -5855,6 +6561,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -5881,6 +6592,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -5907,6 +6623,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -5933,6 +6654,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -5959,6 +6685,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -5985,6 +6716,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -6011,6 +6747,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -6037,6 +6778,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -6063,6 +6809,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -6089,6 +6840,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -6115,6 +6871,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -6141,6 +6902,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -6167,6 +6933,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -6193,6 +6960,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -6219,6 +6987,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -6245,6 +7014,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -6271,6 +7041,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -6297,6 +7068,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -6323,6 +7095,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -6349,6 +7122,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -6375,6 +7149,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -6401,6 +7176,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -6427,6 +7203,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -6453,6 +7230,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -6479,6 +7257,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -6505,6 +7284,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -6531,6 +7311,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -6557,6 +7338,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -6583,6 +7365,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -6609,6 +7392,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -6635,6 +7419,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -6661,6 +7446,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -6687,6 +7473,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -6713,6 +7500,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -6739,6 +7527,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -6765,6 +7554,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -6791,6 +7581,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -6817,6 +7608,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -6843,6 +7635,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -6869,6 +7662,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -6895,6 +7689,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -6921,6 +7716,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -6947,6 +7743,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -6973,6 +7770,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -6999,6 +7797,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -7025,6 +7824,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -7051,6 +7851,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -7077,6 +7878,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -7103,6 +7905,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -7129,6 +7932,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -7155,6 +7959,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -7181,6 +7986,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -7207,6 +8013,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -7233,6 +8040,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -7259,6 +8067,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -7285,6 +8094,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -7309,6 +8123,11 @@
       <c r="F115" s="5" t="inlineStr">
         <is>
           <t>OP_LOGE</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
         </is>
       </c>
     </row>
@@ -7323,7 +8142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F270"/>
+  <dimension ref="A1:G270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -7365,6 +8184,11 @@
           <t>日志类型</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -7391,6 +8215,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -7417,6 +8246,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -7443,6 +8277,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -7469,6 +8308,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -7495,6 +8339,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -7521,6 +8370,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -7547,6 +8401,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -7573,6 +8432,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -7599,6 +8463,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -7625,6 +8494,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -7651,6 +8525,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -7677,6 +8556,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -7703,6 +8587,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -7729,6 +8618,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -7755,6 +8649,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -7781,6 +8680,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -7807,6 +8711,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -7833,6 +8742,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -7859,6 +8773,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -7885,6 +8804,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -7911,6 +8835,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -7937,6 +8866,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -7963,6 +8897,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -7989,6 +8928,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -8015,6 +8959,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -8041,6 +8990,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -8067,6 +9021,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -8093,6 +9052,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -8119,6 +9083,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -8145,6 +9114,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -8171,6 +9145,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -8197,6 +9176,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -8223,6 +9207,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -8249,6 +9238,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -8275,6 +9269,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -8301,6 +9300,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -8327,6 +9331,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -8353,6 +9362,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -8379,6 +9393,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -8405,6 +9424,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -8431,6 +9455,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -8457,6 +9486,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -8483,6 +9517,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -8509,6 +9548,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -8535,6 +9579,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -8561,6 +9610,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -8587,6 +9641,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -8613,6 +9672,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -8639,6 +9703,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -8665,6 +9734,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -8691,6 +9765,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -8717,6 +9796,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -8743,6 +9827,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -8769,6 +9858,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -8795,6 +9889,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -8821,6 +9920,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -8847,6 +9951,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -8873,6 +9982,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -8899,6 +10013,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -8925,6 +10044,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -8951,6 +10075,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -8977,6 +10106,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -9003,6 +10137,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -9029,6 +10168,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -9055,6 +10199,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -9081,6 +10230,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -9107,6 +10261,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -9133,6 +10292,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -9159,6 +10323,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -9185,6 +10354,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -9211,6 +10385,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -9237,6 +10416,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -9263,6 +10447,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -9289,6 +10478,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -9315,6 +10509,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -9341,6 +10540,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -9367,6 +10571,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -9393,6 +10602,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -9419,6 +10633,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -9445,6 +10664,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -9471,6 +10695,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -9497,6 +10726,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -9523,6 +10757,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -9549,6 +10788,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -9575,6 +10819,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -9601,6 +10850,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -9627,6 +10881,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -9653,6 +10912,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -9679,6 +10943,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -9705,6 +10974,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -9731,6 +11005,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -9757,6 +11036,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -9783,6 +11067,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -9809,6 +11098,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -9835,6 +11129,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -9861,6 +11160,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -9887,6 +11191,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -9913,6 +11222,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -9939,6 +11253,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -9965,6 +11284,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -9991,6 +11315,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -10017,6 +11346,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -10043,6 +11377,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -10069,6 +11408,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -10095,6 +11439,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -10121,6 +11470,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -10147,6 +11501,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -10173,6 +11532,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -10199,6 +11563,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -10225,6 +11594,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -10251,6 +11625,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -10277,6 +11656,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -10303,6 +11687,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -10329,6 +11718,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -10355,6 +11749,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -10381,6 +11780,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -10407,6 +11811,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -10433,6 +11842,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -10459,6 +11873,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -10485,6 +11904,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -10511,6 +11935,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -10537,6 +11966,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -10563,6 +11997,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -10589,6 +12028,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -10615,6 +12059,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -10641,6 +12090,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -10667,6 +12121,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -10693,6 +12152,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -10719,6 +12183,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -10745,6 +12214,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -10771,6 +12245,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
@@ -10797,6 +12276,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -10823,6 +12307,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -10849,6 +12338,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -10875,6 +12369,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
@@ -10901,6 +12400,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -10927,6 +12431,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -10953,6 +12458,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -10979,6 +12485,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -11005,6 +12512,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -11031,6 +12539,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -11057,6 +12566,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -11083,6 +12593,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
@@ -11109,6 +12620,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -11135,6 +12647,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
@@ -11161,6 +12674,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -11187,6 +12701,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -11213,6 +12728,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -11239,6 +12755,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
@@ -11265,6 +12782,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -11291,6 +12809,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
@@ -11317,6 +12836,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
@@ -11343,6 +12863,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
@@ -11369,6 +12890,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
@@ -11395,6 +12917,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
@@ -11421,6 +12944,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
@@ -11447,6 +12971,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -11473,6 +12998,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
@@ -11499,6 +13025,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
@@ -11525,6 +13052,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="5" t="inlineStr">
@@ -11551,6 +13079,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
@@ -11577,6 +13106,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -11603,6 +13133,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
@@ -11629,6 +13160,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
@@ -11655,6 +13187,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
@@ -11681,6 +13214,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
@@ -11707,6 +13241,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
@@ -11733,6 +13268,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
@@ -11759,6 +13295,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
@@ -11785,6 +13322,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -11811,6 +13349,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
@@ -11837,6 +13376,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
@@ -11863,6 +13403,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
@@ -11889,6 +13430,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
@@ -11915,6 +13457,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
@@ -11941,6 +13484,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
@@ -11967,6 +13511,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
@@ -11993,6 +13538,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
@@ -12019,6 +13565,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
@@ -12045,6 +13592,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
@@ -12071,6 +13619,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
@@ -12097,6 +13646,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
@@ -12123,6 +13673,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
@@ -12149,6 +13700,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
@@ -12175,6 +13727,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
@@ -12201,6 +13754,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
@@ -12227,6 +13781,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
@@ -12253,6 +13808,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
@@ -12279,6 +13835,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
@@ -12305,6 +13862,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
@@ -12331,6 +13889,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="5" t="inlineStr">
@@ -12357,6 +13916,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="5" t="inlineStr">
@@ -12383,6 +13943,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="5" t="inlineStr">
@@ -12409,6 +13970,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="5" t="inlineStr">
@@ -12435,6 +13997,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
@@ -12461,6 +14024,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="5" t="inlineStr">
@@ -12487,6 +14051,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="5" t="inlineStr">
@@ -12513,6 +14078,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
@@ -12539,6 +14105,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="5" t="inlineStr">
@@ -12565,6 +14132,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
@@ -12591,6 +14159,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
@@ -12617,6 +14186,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="5" t="inlineStr">
@@ -12643,6 +14213,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
@@ -12669,6 +14240,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
@@ -12695,6 +14267,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
@@ -12721,6 +14294,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
@@ -12747,6 +14321,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="5" t="inlineStr">
@@ -12773,6 +14348,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
@@ -12799,6 +14375,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
@@ -12825,6 +14402,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="5" t="inlineStr">
@@ -12851,6 +14429,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
@@ -12877,6 +14456,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
@@ -12903,6 +14483,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
@@ -12929,6 +14510,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
@@ -12955,6 +14537,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
@@ -12981,6 +14564,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="5" t="inlineStr">
@@ -13007,6 +14591,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="5" t="inlineStr">
@@ -13033,6 +14618,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
@@ -13059,6 +14645,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
@@ -13085,6 +14672,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
@@ -13111,6 +14699,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
@@ -13137,6 +14726,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="5" t="inlineStr">
@@ -13163,6 +14753,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="5" t="inlineStr">
@@ -13189,6 +14780,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="5" t="inlineStr">
@@ -13215,6 +14807,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="5" t="inlineStr">
@@ -13241,6 +14834,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
@@ -13267,6 +14861,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
@@ -13293,6 +14888,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
@@ -13319,6 +14915,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
@@ -13345,6 +14942,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
@@ -13371,6 +14969,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
@@ -13397,6 +14996,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
@@ -13423,6 +15023,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
@@ -13449,6 +15050,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
@@ -13475,6 +15077,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
@@ -13501,6 +15104,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="5" t="inlineStr">
@@ -13527,6 +15131,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="5" t="inlineStr">
@@ -13553,6 +15158,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="5" t="inlineStr">
@@ -13579,6 +15185,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="5" t="inlineStr">
@@ -13605,6 +15212,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
@@ -13631,6 +15239,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
@@ -13657,6 +15266,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
@@ -13683,6 +15293,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="5" t="inlineStr">
@@ -13709,6 +15320,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="5" t="inlineStr">
@@ -13735,6 +15347,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="5" t="inlineStr">
@@ -13761,6 +15374,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="5" t="inlineStr">
@@ -13787,6 +15401,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
@@ -13813,6 +15428,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="5" t="inlineStr">
@@ -13839,6 +15455,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="5" t="inlineStr">
@@ -13865,6 +15482,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="5" t="inlineStr">
@@ -13891,6 +15509,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="5" t="inlineStr">
@@ -13917,6 +15536,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="5" t="inlineStr">
@@ -13943,6 +15563,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="5" t="inlineStr">
@@ -13969,6 +15590,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
@@ -13995,6 +15617,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
@@ -14021,6 +15644,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
@@ -14047,6 +15671,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
@@ -14073,6 +15698,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="5" t="inlineStr">
@@ -14099,6 +15725,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="5" t="inlineStr">
@@ -14125,6 +15752,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="5" t="inlineStr">
@@ -14151,6 +15779,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="5" t="inlineStr">
@@ -14177,6 +15806,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="5" t="inlineStr">
@@ -14203,6 +15833,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="5" t="inlineStr">
@@ -14229,6 +15860,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="5" t="inlineStr">
@@ -14255,6 +15887,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="5" t="inlineStr">
@@ -14281,6 +15918,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="5" t="inlineStr">
@@ -14307,6 +15949,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="5" t="inlineStr">
@@ -14333,6 +15980,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="5" t="inlineStr">
@@ -14357,6 +16009,11 @@
       <c r="F270" s="5" t="inlineStr">
         <is>
           <t>OP_LOGE</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
         </is>
       </c>
     </row>
@@ -14371,7 +16028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -14413,6 +16070,11 @@
           <t>日志类型</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -14439,6 +16101,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -14465,6 +16128,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -14491,6 +16159,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -14517,6 +16190,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -14543,6 +16221,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -14569,6 +16252,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -14595,6 +16283,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -14621,6 +16314,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -14647,6 +16345,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -14673,6 +16376,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -14699,6 +16407,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -14725,6 +16438,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -14751,6 +16469,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -14777,6 +16500,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -14803,6 +16531,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -14829,6 +16562,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -14855,6 +16593,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -14881,6 +16624,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -14907,6 +16655,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -14933,6 +16686,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -14959,6 +16717,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -14985,6 +16748,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -15011,6 +16779,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -15037,6 +16810,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -15063,6 +16841,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -15089,6 +16872,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -15115,6 +16903,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -15141,6 +16934,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -15167,6 +16965,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -15193,6 +16996,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -15219,6 +17027,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -15245,6 +17058,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -15271,6 +17089,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -15297,6 +17120,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -15323,6 +17151,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -15349,6 +17182,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -15375,6 +17213,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -15401,6 +17244,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -15427,6 +17275,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -15453,6 +17306,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -15479,6 +17337,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -15505,6 +17368,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -15531,6 +17399,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -15557,6 +17430,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -15583,6 +17461,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -15609,6 +17492,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -15635,6 +17523,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -15661,6 +17554,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -15687,6 +17585,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -15713,6 +17616,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -15739,6 +17647,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -15765,6 +17678,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -15791,6 +17709,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -15817,6 +17740,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -15843,6 +17771,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -15869,6 +17802,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -15895,6 +17833,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -15921,6 +17860,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -15947,6 +17887,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -15973,6 +17914,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -15999,6 +17941,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -16025,6 +17968,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -16051,6 +17995,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -16077,6 +18022,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -16103,6 +18049,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -16129,6 +18076,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -16155,6 +18103,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -16181,6 +18130,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -16207,6 +18157,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -16233,6 +18184,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -16259,6 +18211,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -16285,6 +18238,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -16311,6 +18265,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -16337,6 +18292,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -16363,6 +18319,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -16387,6 +18344,11 @@
       <c r="F77" s="5" t="inlineStr">
         <is>
           <t>OP_LOGE</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
         </is>
       </c>
     </row>
@@ -16401,7 +18363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:G137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -16443,6 +18405,11 @@
           <t>日志类型</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -16469,6 +18436,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -16495,6 +18463,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -16521,6 +18490,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -16547,6 +18517,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -16573,6 +18544,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -16599,6 +18571,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -16625,6 +18598,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -16651,6 +18625,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -16677,6 +18652,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -16703,6 +18679,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -16729,6 +18706,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -16755,6 +18737,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -16781,6 +18768,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -16807,6 +18799,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -16833,6 +18830,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -16859,6 +18861,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -16885,6 +18892,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -16911,6 +18923,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -16937,6 +18954,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -16963,6 +18985,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -16989,6 +19016,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -17015,6 +19047,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -17041,6 +19078,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -17067,6 +19109,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -17093,6 +19140,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -17119,6 +19171,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -17145,6 +19202,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -17171,6 +19233,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -17197,6 +19264,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -17223,6 +19295,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -17249,6 +19326,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -17275,6 +19357,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -17301,6 +19388,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -17327,6 +19419,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -17353,6 +19450,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -17379,6 +19481,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -17405,6 +19512,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -17431,6 +19543,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -17457,6 +19574,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -17483,6 +19605,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -17509,6 +19636,11 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -17535,6 +19667,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -17561,6 +19694,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -17587,6 +19721,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -17613,6 +19752,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -17639,6 +19783,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -17665,6 +19814,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -17691,6 +19845,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -17717,6 +19876,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -17743,6 +19907,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -17769,6 +19938,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -17795,6 +19969,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -17821,6 +20000,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -17847,6 +20031,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -17873,6 +20062,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -17899,6 +20093,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -17925,6 +20124,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -17951,6 +20155,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -17977,6 +20186,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -18003,6 +20217,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -18029,6 +20248,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -18055,6 +20279,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -18081,6 +20310,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -18107,6 +20341,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -18133,6 +20372,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -18159,6 +20403,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -18185,6 +20434,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -18211,6 +20465,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -18237,6 +20496,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -18263,6 +20527,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -18289,6 +20558,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -18315,6 +20589,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -18341,6 +20620,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -18367,6 +20651,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -18393,6 +20682,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -18419,6 +20713,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -18445,6 +20744,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -18471,6 +20775,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -18497,6 +20806,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -18523,6 +20837,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -18549,6 +20868,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -18575,6 +20899,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -18601,6 +20926,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -18627,6 +20953,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -18653,6 +20980,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -18679,6 +21007,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -18705,6 +21034,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -18731,6 +21061,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -18757,6 +21088,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -18783,6 +21115,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -18809,6 +21142,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -18835,6 +21169,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -18861,6 +21196,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -18887,6 +21223,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -18913,6 +21250,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -18939,6 +21277,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -18965,6 +21304,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -18991,6 +21331,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -19017,6 +21358,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -19043,6 +21385,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -19069,6 +21412,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -19095,6 +21439,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -19121,6 +21466,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -19147,6 +21493,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -19173,6 +21520,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -19199,6 +21547,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -19225,6 +21574,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -19251,6 +21601,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -19277,6 +21628,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -19303,6 +21655,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -19329,6 +21682,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -19355,6 +21709,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -19381,6 +21736,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -19407,6 +21763,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -19433,6 +21790,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -19459,6 +21817,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -19485,6 +21844,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -19511,6 +21871,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -19537,6 +21898,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -19563,6 +21925,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -19589,6 +21952,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -19615,6 +21979,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -19641,6 +22006,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -19667,6 +22033,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -19693,6 +22060,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -19719,6 +22087,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -19745,6 +22114,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -19771,6 +22141,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -19797,6 +22168,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
@@ -19823,6 +22195,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -19849,6 +22222,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
@@ -19875,6 +22249,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -19901,6 +22276,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
@@ -19927,6 +22303,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -19953,6 +22330,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
@@ -19979,6 +22357,7 @@
           <t>OPS_REPORT_VECTOR_INNER_ERR</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19991,7 +22370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -20033,6 +22412,11 @@
           <t>日志类型</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -20059,6 +22443,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -20085,6 +22470,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -20111,6 +22501,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -20137,6 +22532,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -20163,6 +22563,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20175,7 +22576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -20217,6 +22618,11 @@
           <t>日志类型</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>归属</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -20243,6 +22649,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -20269,6 +22676,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -20295,6 +22703,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -20321,6 +22730,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -20347,6 +22757,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -20373,6 +22788,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -20399,6 +22819,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -20425,6 +22850,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -20451,6 +22881,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -20477,6 +22912,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -20503,6 +22943,11 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ifa@ops-transformer</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -20529,6 +22974,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -20555,6 +23001,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -20581,6 +23028,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -20607,6 +23055,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -20633,6 +23082,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -20659,6 +23109,7 @@
           <t>OP_LOGE</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
